--- a/Data/billing_template.xlsx
+++ b/Data/billing_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\test\Gen\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D256943D-4B3F-459A-9F8C-861528A2159A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DAF461-7064-4C2F-8BA8-AE31025017B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -37,16 +37,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -54,12 +66,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,23 +466,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>9981584725</v>
+    <row r="2" spans="1:1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>9981473853</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+    </row>
+    <row r="4" spans="1:1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>

--- a/Data/billing_template.xlsx
+++ b/Data/billing_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\test\Gen\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DAF461-7064-4C2F-8BA8-AE31025017B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFF4F1D-F76A-45B7-92FD-CC100280FD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5340" yWindow="1140" windowWidth="11472" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BA List" sheetId="1" r:id="rId1"/>
@@ -38,10 +38,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Segoe UI"/>
+      <name val="Tahoma"/>
       <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,57 +59,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFD3D3D3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFD3D3D3"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFD3D3D3"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFD3D3D3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFD3D3D3"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFCCCCCC"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFD3D3D3"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFD3D3D3"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFCCCCCC"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FFD3D3D3"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -117,14 +73,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -465,27 +421,116 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
-        <v>9981473853</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="4" spans="1:1" ht="15.6" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3"/>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>9981948092</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>9988962667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>9983117405</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>9988844347</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>9986619730</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>9981644279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>9982028868</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>9988973483</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9982768935</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>9982584509</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>9985671882</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>9987361812</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>9984831342</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>9986992462</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>9985999331</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>9987800512</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>9984993127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>9987860196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>9981756596</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>9989353919</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/billing_template.xlsx
+++ b/Data/billing_template.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\test\Gen\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FFF4F1D-F76A-45B7-92FD-CC100280FD21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7801E5CE-0DEC-4FFF-A17F-88A644383B3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5340" yWindow="1140" windowWidth="11472" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BA List" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -29,7 +42,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -38,28 +54,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Tahoma"/>
       <family val="2"/>
-      <scheme val="major"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -67,24 +81,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Comma 2" xfId="2" xr:uid="{98F9EC48-E809-4F23-9A9E-F3CCC167F962}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{A6AF1A13-9021-4A37-8894-ED952EDBF07B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -421,115 +451,615 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A21"/>
+  <dimension ref="A1:A121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2">
-        <v>9981948092</v>
+      <c r="A2" s="2">
+        <v>9982568066</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>9988962667</v>
+        <v>9988598357</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
-        <v>9983117405</v>
+        <v>9987919827</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>9988844347</v>
+      <c r="A5" s="2">
+        <v>9985295324</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>9986619730</v>
+      <c r="A6" s="2">
+        <v>9984862299</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>9981644279</v>
+      <c r="A7" s="2">
+        <v>9989493020</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>9982028868</v>
+      <c r="A8" s="2">
+        <v>9981893316</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>9988973483</v>
+      <c r="A9" s="2">
+        <v>9986575157</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9982768935</v>
+      <c r="A10" s="2">
+        <v>9989778272</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>9982584509</v>
+      <c r="A11" s="2">
+        <v>9989608118</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>9985671882</v>
+      <c r="A12" s="2">
+        <v>9983667028</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>9987361812</v>
+      <c r="A13" s="2">
+        <v>9986273039</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>9984831342</v>
+      <c r="A14" s="2">
+        <v>9986089270</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>9986992462</v>
+      <c r="A15" s="2">
+        <v>9982805428</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>9985999331</v>
+      <c r="A16" s="2">
+        <v>9987876262</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17">
-        <v>9987800512</v>
+      <c r="A17" s="2">
+        <v>9988123560</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>9984993127</v>
+      <c r="A18" s="2">
+        <v>9984460272</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>9987860196</v>
+      <c r="A19" s="2">
+        <v>9989970142</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20">
-        <v>9981756596</v>
+      <c r="A20" s="2">
+        <v>9987451344</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>9989353919</v>
+      <c r="A21" s="2">
+        <v>9986898813</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>9985333985</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>9984011395</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>9987187111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>9986675390</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>9988179313</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>9981166926</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>9985085531</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <v>9989075809</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>9989859914</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <v>9988833077</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>9985338033</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <v>9988494746</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <v>9987173153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <v>9988494915</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>9984222256</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <v>9981424216</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>9988240721</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <v>9987672061</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <v>9982443381</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <v>9985450842</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <v>9987825274</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <v>9983135070</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>9984299434</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <v>9983164845</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <v>9989359386</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <v>9982085823</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <v>9982378899</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <v>9987759998</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>9986301772</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <v>9982477295</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>9989263974</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53" s="2">
+        <v>9983371641</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
+        <v>9984331105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2">
+        <v>9985518458</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
+        <v>9981912082</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>9984615247</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>9987628015</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>9988686038</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>9986840122</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>9989240022</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>9982754456</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>9983097445</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
+        <v>9988129782</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2">
+        <v>9985686476</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
+        <v>9986497291</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2">
+        <v>9985671449</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
+        <v>9986255138</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2">
+        <v>9984251749</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
+        <v>9981275907</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71" s="2">
+        <v>9989696186</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>9982326267</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73" s="2">
+        <v>9985320988</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>9989246914</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>9986934952</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>9988499544</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>9985553057</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>9982199270</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>9984407049</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
+        <v>9987835965</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81" s="2">
+        <v>9989790244</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
+        <v>9987424037</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83" s="2">
+        <v>9988015693</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
+        <v>9985007142</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85" s="2">
+        <v>9983134421</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
+        <v>9986013937</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87" s="2">
+        <v>9986383785</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>9987900204</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>9981616189</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>9989074118</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
+        <v>9988955189</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
+        <v>9984386085</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>9988020346</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>9987898206</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>9985549594</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>9983645749</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>9988312144</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>9989628142</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>9984213140</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>9983988898</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>9986365438</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>9987362319</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>9985568318</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>9987871677</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>9987672719</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>9987483923</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>9981104413</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>9987162791</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>9985120720</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>9983587139</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>9983195119</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>9989298561</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>9986023468</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>9989691690</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>9987449009</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>9981129218</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>9981543348</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>9987585924</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A119" s="2">
+        <v>9981778751</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A120" s="2">
+        <v>9984455948</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A121" s="2">
+        <v>9987727564</v>
       </c>
     </row>
   </sheetData>
